--- a/experiments/hybrid_results/comparison.xlsx
+++ b/experiments/hybrid_results/comparison.xlsx
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32.41423916816711</v>
+        <v>51.30514430999756</v>
       </c>
       <c r="D2" t="n">
         <v>0.9904761904761904</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33.87127470970154</v>
+        <v>57.47790265083313</v>
       </c>
       <c r="D3" t="n">
         <v>0.5892053973013494</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.36446332931519</v>
+        <v>41.25898361206055</v>
       </c>
       <c r="D4" t="n">
         <v>0.6785001994415636</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51.31387209892273</v>
+        <v>76.41990923881531</v>
       </c>
       <c r="D5" t="n">
         <v>0.9731139646869983</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24.52415585517883</v>
+        <v>39.33284878730774</v>
       </c>
       <c r="D6" t="n">
         <v>0.7209690893901419</v>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.42279624938965</v>
+        <v>51.97054862976074</v>
       </c>
       <c r="D7" t="n">
         <v>0.8617857142857143</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52.12599420547485</v>
+        <v>81.76472687721252</v>
       </c>
       <c r="D8" t="n">
         <v>0.9949048913043478</v>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26.29757475852966</v>
+        <v>40.0873658657074</v>
       </c>
       <c r="D9" t="n">
         <v>0.7702834799608993</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35.49734306335449</v>
+        <v>55.40466570854187</v>
       </c>
       <c r="D10" t="n">
         <v>0.7291325695581015</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.49714803695679</v>
+        <v>36.46507453918457</v>
       </c>
       <c r="D11" t="n">
         <v>0.5372002459520393</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47.64908885955811</v>
+        <v>75.10465312004089</v>
       </c>
       <c r="D12" t="n">
         <v>0.9898989898989898</v>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.52682280540466</v>
+        <v>26.94470262527466</v>
       </c>
       <c r="D13" t="n">
         <v>0.8666666666666666</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.68641471862793</v>
+        <v>45.3782958984375</v>
       </c>
       <c r="D14" t="n">
         <v>0.7925</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.60031723976135</v>
+        <v>60.02826571464539</v>
       </c>
       <c r="D15" t="n">
         <v>0.9982456140350878</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42.04572820663452</v>
+        <v>65.27954649925232</v>
       </c>
       <c r="D16" t="n">
         <v>0.8946953781512604</v>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.508202075958252</v>
+        <v>7.359907627105713</v>
       </c>
       <c r="D17" t="n">
         <v>0.9904761904761904</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.663533687591553</v>
+        <v>18.55292558670044</v>
       </c>
       <c r="D18" t="n">
         <v>0.5892053973013494</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.813713073730469</v>
+        <v>16.19871759414673</v>
       </c>
       <c r="D19" t="n">
         <v>0.6785001994415636</v>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.115579843521118</v>
+        <v>15.0835120677948</v>
       </c>
       <c r="D20" t="n">
         <v>0.9731139646869983</v>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.590111970901489</v>
+        <v>6.530462503433228</v>
       </c>
       <c r="D21" t="n">
         <v>0.7209690893901419</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.198394775390625</v>
+        <v>13.41936802864075</v>
       </c>
       <c r="D22" t="n">
         <v>0.8617857142857143</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.991473436355591</v>
+        <v>14.49900650978088</v>
       </c>
       <c r="D23" t="n">
         <v>0.9949048913043478</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.195052862167358</v>
+        <v>7.405401229858398</v>
       </c>
       <c r="D24" t="n">
         <v>0.7702834799608993</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.987757444381714</v>
+        <v>12.12524437904358</v>
       </c>
       <c r="D25" t="n">
         <v>0.7291325695581015</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.781319379806519</v>
+        <v>10.52671909332275</v>
       </c>
       <c r="D26" t="n">
         <v>0.5372002459520393</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.120864629745483</v>
+        <v>10.74446105957031</v>
       </c>
       <c r="D27" t="n">
         <v>0.9898989898989898</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.164411544799805</v>
+        <v>7.893769979476929</v>
       </c>
       <c r="D28" t="n">
         <v>0.8666666666666666</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.493779897689819</v>
+        <v>13.91463541984558</v>
       </c>
       <c r="D29" t="n">
         <v>0.7925</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.67671537399292</v>
+        <v>12.77880120277405</v>
       </c>
       <c r="D30" t="n">
         <v>0.9982456140350878</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.40549373626709</v>
+        <v>9.656274080276489</v>
       </c>
       <c r="D31" t="n">
         <v>0.8946953781512604</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>39.22007751464844</v>
+        <v>44.32058143615723</v>
       </c>
       <c r="D32" t="n">
         <v>0.946031746031746</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>70.45853900909424</v>
+        <v>84.85165929794312</v>
       </c>
       <c r="D33" t="n">
         <v>0.8746251874062968</v>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>62.24064898490906</v>
+        <v>75.02032446861267</v>
       </c>
       <c r="D34" t="n">
         <v>0.7742321499800559</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>53.42201662063599</v>
+        <v>67.64461803436279</v>
       </c>
       <c r="D35" t="n">
         <v>0.804975922953451</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35.95851135253906</v>
+        <v>72.66959953308105</v>
       </c>
       <c r="D36" t="n">
         <v>0.9883040935672514</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50.55043768882751</v>
+        <v>79.14483261108398</v>
       </c>
       <c r="D37" t="n">
         <v>0.8746428571428572</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>56.85665345191956</v>
+        <v>90.45528364181519</v>
       </c>
       <c r="D38" t="n">
         <v>0.9391983695652174</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50.4085898399353</v>
+        <v>79.20102906227112</v>
       </c>
       <c r="D39" t="n">
         <v>0.9227761485826002</v>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>73.54312992095947</v>
+        <v>115.395409822464</v>
       </c>
       <c r="D40" t="n">
         <v>0.8161483906164757</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>70.31767320632935</v>
+        <v>110.9897994995117</v>
       </c>
       <c r="D41" t="n">
         <v>0.6423447427751587</v>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>53.57215332984924</v>
+        <v>84.03663206100464</v>
       </c>
       <c r="D42" t="n">
         <v>0.8823953823953824</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21.27709984779358</v>
+        <v>34.21918678283691</v>
       </c>
       <c r="D43" t="n">
         <v>0.888888888888889</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>46.0355212688446</v>
+        <v>74.5580620765686</v>
       </c>
       <c r="D44" t="n">
         <v>0.79625</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37.21659588813782</v>
+        <v>59.26060914993286</v>
       </c>
       <c r="D45" t="n">
         <v>0.8280701754385965</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>65.00382900238037</v>
+        <v>99.73568224906921</v>
       </c>
       <c r="D46" t="n">
         <v>0.8529411764705882</v>

--- a/experiments/hybrid_results/comparison.xlsx
+++ b/experiments/hybrid_results/comparison.xlsx
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51.30514430999756</v>
+        <v>33.69089436531067</v>
       </c>
       <c r="D2" t="n">
         <v>0.9904761904761904</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.47790265083313</v>
+        <v>35.70123267173767</v>
       </c>
       <c r="D3" t="n">
         <v>0.5892053973013494</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.25898361206055</v>
+        <v>28.27394533157349</v>
       </c>
       <c r="D4" t="n">
         <v>0.6785001994415636</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.41990923881531</v>
+        <v>53.5795738697052</v>
       </c>
       <c r="D5" t="n">
         <v>0.9731139646869983</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39.33284878730774</v>
+        <v>25.43543982505798</v>
       </c>
       <c r="D6" t="n">
         <v>0.7209690893901419</v>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51.97054862976074</v>
+        <v>33.66065096855164</v>
       </c>
       <c r="D7" t="n">
         <v>0.8617857142857143</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>81.76472687721252</v>
+        <v>55.29569458961487</v>
       </c>
       <c r="D8" t="n">
         <v>0.9949048913043478</v>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40.0873658657074</v>
+        <v>27.92267990112305</v>
       </c>
       <c r="D9" t="n">
         <v>0.7702834799608993</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.40466570854187</v>
+        <v>38.34892272949219</v>
       </c>
       <c r="D10" t="n">
         <v>0.7291325695581015</v>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.46507453918457</v>
+        <v>24.80258131027222</v>
       </c>
       <c r="D11" t="n">
         <v>0.5372002459520393</v>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75.10465312004089</v>
+        <v>49.58110642433167</v>
       </c>
       <c r="D12" t="n">
         <v>0.9898989898989898</v>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.94470262527466</v>
+        <v>16.70360016822815</v>
       </c>
       <c r="D13" t="n">
         <v>0.8666666666666666</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>45.3782958984375</v>
+        <v>27.43989968299866</v>
       </c>
       <c r="D14" t="n">
         <v>0.7925</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60.02826571464539</v>
+        <v>38.69757103919983</v>
       </c>
       <c r="D15" t="n">
         <v>0.9982456140350878</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>65.27954649925232</v>
+        <v>43.44195437431335</v>
       </c>
       <c r="D16" t="n">
         <v>0.8946953781512604</v>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.359907627105713</v>
+        <v>5.373984098434448</v>
       </c>
       <c r="D17" t="n">
         <v>0.9904761904761904</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18.55292558670044</v>
+        <v>11.21445751190186</v>
       </c>
       <c r="D18" t="n">
         <v>0.5892053973013494</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.19871759414673</v>
+        <v>10.36502885818481</v>
       </c>
       <c r="D19" t="n">
         <v>0.6785001994415636</v>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15.0835120677948</v>
+        <v>9.483864784240723</v>
       </c>
       <c r="D20" t="n">
         <v>0.9731139646869983</v>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.530462503433228</v>
+        <v>4.586628198623657</v>
       </c>
       <c r="D21" t="n">
         <v>0.7209690893901419</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13.41936802864075</v>
+        <v>8.312727451324463</v>
       </c>
       <c r="D22" t="n">
         <v>0.8617857142857143</v>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.49900650978088</v>
+        <v>9.196866989135742</v>
       </c>
       <c r="D23" t="n">
         <v>0.9949048913043478</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.405401229858398</v>
+        <v>4.941753387451172</v>
       </c>
       <c r="D24" t="n">
         <v>0.7702834799608993</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12.12524437904358</v>
+        <v>8.06245231628418</v>
       </c>
       <c r="D25" t="n">
         <v>0.7291325695581015</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.52671909332275</v>
+        <v>6.99725604057312</v>
       </c>
       <c r="D26" t="n">
         <v>0.5372002459520393</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10.74446105957031</v>
+        <v>6.968843460083008</v>
       </c>
       <c r="D27" t="n">
         <v>0.9898989898989898</v>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.893769979476929</v>
+        <v>4.923839569091797</v>
       </c>
       <c r="D28" t="n">
         <v>0.8666666666666666</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13.91463541984558</v>
+        <v>8.609135627746582</v>
       </c>
       <c r="D29" t="n">
         <v>0.7925</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12.77880120277405</v>
+        <v>7.609845161437988</v>
       </c>
       <c r="D30" t="n">
         <v>0.9982456140350878</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.656274080276489</v>
+        <v>6.432675123214722</v>
       </c>
       <c r="D31" t="n">
         <v>0.8946953781512604</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>44.32058143615723</v>
+        <v>38.11904954910278</v>
       </c>
       <c r="D32" t="n">
         <v>0.946031746031746</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>84.85165929794312</v>
+        <v>70.24255657196045</v>
       </c>
       <c r="D33" t="n">
         <v>0.8746251874062968</v>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>75.02032446861267</v>
+        <v>62.75869917869568</v>
       </c>
       <c r="D34" t="n">
         <v>0.7742321499800559</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>67.64461803436279</v>
+        <v>55.70905876159668</v>
       </c>
       <c r="D35" t="n">
         <v>0.804975922953451</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>72.66959953308105</v>
+        <v>37.35616588592529</v>
       </c>
       <c r="D36" t="n">
         <v>0.9883040935672514</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>79.14483261108398</v>
+        <v>52.63231182098389</v>
       </c>
       <c r="D37" t="n">
         <v>0.8746428571428572</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>90.45528364181519</v>
+        <v>58.6241180896759</v>
       </c>
       <c r="D38" t="n">
         <v>0.9391983695652174</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>79.20102906227112</v>
+        <v>52.63049077987671</v>
       </c>
       <c r="D39" t="n">
         <v>0.9227761485826002</v>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>115.395409822464</v>
+        <v>76.12669992446899</v>
       </c>
       <c r="D40" t="n">
         <v>0.8161483906164757</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>110.9897994995117</v>
+        <v>73.18037152290344</v>
       </c>
       <c r="D41" t="n">
         <v>0.6423447427751587</v>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>84.03663206100464</v>
+        <v>56.2178840637207</v>
       </c>
       <c r="D42" t="n">
         <v>0.8823953823953824</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>34.21918678283691</v>
+        <v>21.95231103897095</v>
       </c>
       <c r="D43" t="n">
         <v>0.888888888888889</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>74.5580620765686</v>
+        <v>48.09749269485474</v>
       </c>
       <c r="D44" t="n">
         <v>0.79625</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>59.26060914993286</v>
+        <v>40.04155468940735</v>
       </c>
       <c r="D45" t="n">
         <v>0.8280701754385965</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>99.73568224906921</v>
+        <v>68.96778774261475</v>
       </c>
       <c r="D46" t="n">
         <v>0.8529411764705882</v>

--- a/experiments/hybrid_results/comparison.xlsx
+++ b/experiments/hybrid_results/comparison.xlsx
@@ -10,7 +10,9 @@
     <sheet name="image_auroc" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="pixel_e2e_auroc" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="pixel_cond_auroc" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="anomaly_pass_rate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="normal_pass_rate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="raw" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,7 +465,7 @@
         <v>0.9904761904761904</v>
       </c>
       <c r="C2" t="n">
-        <v>0.946031746031746</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0.9904761904761904</v>
@@ -479,7 +481,7 @@
         <v>0.5892053973013494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8746251874062968</v>
+        <v>0.9419040479760119</v>
       </c>
       <c r="D3" t="n">
         <v>0.5892053973013494</v>
@@ -495,7 +497,7 @@
         <v>0.6785001994415636</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7742321499800559</v>
+        <v>0.9433585959313922</v>
       </c>
       <c r="D4" t="n">
         <v>0.6785001994415636</v>
@@ -511,7 +513,7 @@
         <v>0.9731139646869983</v>
       </c>
       <c r="C5" t="n">
-        <v>0.804975922953451</v>
+        <v>0.9979935794542536</v>
       </c>
       <c r="D5" t="n">
         <v>0.9731139646869983</v>
@@ -527,7 +529,7 @@
         <v>0.7209690893901419</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9883040935672514</v>
+        <v>0.9983291562238931</v>
       </c>
       <c r="D6" t="n">
         <v>0.7209690893901419</v>
@@ -543,7 +545,7 @@
         <v>0.8617857142857143</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8746428571428572</v>
+        <v>0.9964285714285714</v>
       </c>
       <c r="D7" t="n">
         <v>0.8617857142857143</v>
@@ -559,7 +561,7 @@
         <v>0.9949048913043478</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9391983695652174</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0.9949048913043478</v>
@@ -575,7 +577,7 @@
         <v>0.7702834799608993</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9227761485826002</v>
+        <v>0.9965786901270772</v>
       </c>
       <c r="D9" t="n">
         <v>0.7702834799608993</v>
@@ -591,7 +593,7 @@
         <v>0.7291325695581015</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8161483906164757</v>
+        <v>0.9716312056737588</v>
       </c>
       <c r="D10" t="n">
         <v>0.7291325695581015</v>
@@ -607,7 +609,7 @@
         <v>0.5372002459520393</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6423447427751587</v>
+        <v>0.8575527772084444</v>
       </c>
       <c r="D11" t="n">
         <v>0.5372002459520393</v>
@@ -623,7 +625,7 @@
         <v>0.9898989898989898</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8823953823953824</v>
+        <v>0.996031746031746</v>
       </c>
       <c r="D12" t="n">
         <v>0.9898989898989898</v>
@@ -639,7 +641,7 @@
         <v>0.8666666666666666</v>
       </c>
       <c r="C13" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9861111111111112</v>
       </c>
       <c r="D13" t="n">
         <v>0.8666666666666666</v>
@@ -655,7 +657,7 @@
         <v>0.7925</v>
       </c>
       <c r="C14" t="n">
-        <v>0.79625</v>
+        <v>0.97875</v>
       </c>
       <c r="D14" t="n">
         <v>0.7925</v>
@@ -671,7 +673,7 @@
         <v>0.9982456140350878</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8280701754385965</v>
+        <v>0.9903508771929824</v>
       </c>
       <c r="D15" t="n">
         <v>0.9982456140350878</v>
@@ -684,13 +686,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8946953781512604</v>
+        <v>0.8944327731092436</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.9963235294117647</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8946953781512604</v>
+        <v>0.8944327731092436</v>
       </c>
     </row>
   </sheetData>
@@ -731,10 +733,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9837489778310913</v>
+        <v>0.983224793531115</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9720728323926561</v>
+        <v>0.9715503067976653</v>
       </c>
     </row>
     <row r="3">
@@ -744,10 +746,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9489224051900619</v>
+        <v>0.9277140245460854</v>
       </c>
       <c r="C3" t="n">
-        <v>0.696837866446949</v>
+        <v>0.691730395607254</v>
       </c>
     </row>
     <row r="4">
@@ -757,10 +759,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9679745570552247</v>
+        <v>0.9741632146924935</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5843973459545361</v>
+        <v>0.5840716137315201</v>
       </c>
     </row>
     <row r="5">
@@ -770,10 +772,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9848809276006585</v>
+        <v>0.9827717690891338</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9827222339196809</v>
+        <v>0.9805169666245553</v>
       </c>
     </row>
     <row r="6">
@@ -783,10 +785,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9931404679281509</v>
+        <v>0.9918926216301506</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5937434533902246</v>
+        <v>0.5934510889646383</v>
       </c>
     </row>
     <row r="7">
@@ -796,10 +798,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.991372349903992</v>
+        <v>0.9925504519712121</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7894994257999846</v>
+        <v>0.7900289637686492</v>
       </c>
     </row>
     <row r="8">
@@ -809,10 +811,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9892071998212391</v>
+        <v>0.9843365949729397</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9892071998212391</v>
+        <v>0.9843365949729397</v>
       </c>
     </row>
     <row r="9">
@@ -822,10 +824,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9546416657878574</v>
+        <v>0.9610840247009795</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8895458099650471</v>
+        <v>0.8898545732901006</v>
       </c>
     </row>
     <row r="10">
@@ -835,10 +837,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8737203556713243</v>
+        <v>0.8928610100100525</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8102817458112959</v>
+        <v>0.8106569859834467</v>
       </c>
     </row>
     <row r="11">
@@ -848,10 +850,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9550177581942121</v>
+        <v>0.9512719075879584</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5409059583400273</v>
+        <v>0.5407418213648125</v>
       </c>
     </row>
     <row r="12">
@@ -861,10 +863,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9476365729562309</v>
+        <v>0.939210435214603</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9448011901307082</v>
+        <v>0.9363535909536239</v>
       </c>
     </row>
     <row r="13">
@@ -874,10 +876,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9889626240271805</v>
+        <v>0.9874068243729678</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8168450032768682</v>
+        <v>0.8163267842454667</v>
       </c>
     </row>
     <row r="14">
@@ -887,10 +889,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8766902534926941</v>
+        <v>0.8517001588294911</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8796129052316763</v>
+        <v>0.8615116093762567</v>
       </c>
     </row>
     <row r="15">
@@ -900,10 +902,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9492964074598156</v>
+        <v>0.9051632885986193</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9492964074598156</v>
+        <v>0.9051632885986193</v>
       </c>
     </row>
     <row r="16">
@@ -913,10 +915,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9362667856678516</v>
+        <v>0.9310720989574277</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7562861986639395</v>
+        <v>0.7532058469308187</v>
       </c>
     </row>
   </sheetData>
@@ -952,7 +954,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9832494699123072</v>
+        <v>0.9826921593018557</v>
       </c>
     </row>
     <row r="3">
@@ -962,7 +964,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9486585792100932</v>
+        <v>0.9227407565936684</v>
       </c>
     </row>
     <row r="4">
@@ -972,7 +974,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9619582495477651</v>
+        <v>0.9580559228463078</v>
       </c>
     </row>
     <row r="5">
@@ -982,7 +984,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9847839852756669</v>
+        <v>0.9825214604592835</v>
       </c>
     </row>
     <row r="6">
@@ -992,7 +994,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9935288752681102</v>
+        <v>0.9926138097555206</v>
       </c>
     </row>
     <row r="7">
@@ -1002,7 +1004,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.990859909950015</v>
+        <v>0.9920276615334384</v>
       </c>
     </row>
     <row r="8">
@@ -1012,7 +1014,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9892071998212391</v>
+        <v>0.9843365949729397</v>
       </c>
     </row>
     <row r="9">
@@ -1022,7 +1024,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9416100922938329</v>
+        <v>0.9425435656639739</v>
       </c>
     </row>
     <row r="10">
@@ -1032,7 +1034,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8595974535990001</v>
+        <v>0.8607711020256499</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1044,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9650497534110423</v>
+        <v>0.9616371924392504</v>
       </c>
     </row>
     <row r="12">
@@ -1052,7 +1054,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9470648925652922</v>
+        <v>0.9384804076465</v>
       </c>
     </row>
     <row r="13">
@@ -1062,7 +1064,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9834652773397834</v>
+        <v>0.9818461347721047</v>
       </c>
     </row>
     <row r="14">
@@ -1072,7 +1074,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8547616786151689</v>
+        <v>0.8236185049277357</v>
       </c>
     </row>
     <row r="15">
@@ -1082,7 +1084,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9492964074598156</v>
+        <v>0.9051632885986193</v>
       </c>
     </row>
     <row r="16">
@@ -1092,7 +1094,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9302014923354888</v>
+        <v>0.9238806570288861</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,6 +1119,358 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>cable</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.358695652173913</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>capsule</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2477064220183486</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>carpet</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.631578947368421</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hazelnut</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>metal_nut</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pill</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4184397163120567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2016806722689076</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tile</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>toothbrush</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zipper</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.6554621848739496</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>bottle</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>cable</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2586206896551724</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>capsule</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>carpet</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hazelnut</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>metal_nut</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pill</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>screw</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tile</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>toothbrush</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zipper</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>method</t>
         </is>
       </c>
@@ -1127,32 +1481,47 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>n_test</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>auroc_img</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>auroc_pix_e2e</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>auroc_pix_cond</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>flag_rate</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_flagged</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>n_masked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>anomaly_pass_rate</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>normal_pass_rate</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1537,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33.69089436531067</v>
+        <v>32.27287268638611</v>
       </c>
       <c r="D2" t="n">
+        <v>83</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.9904761904761904</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.9720728323926561</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.9832494699123072</v>
+        <v>0.9715503067976653</v>
       </c>
       <c r="G2" t="n">
+        <v>0.9826921593018557</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.7349397590361446</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>61</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>63</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
@@ -1201,25 +1579,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35.70123267173767</v>
+        <v>35.61730575561523</v>
       </c>
       <c r="D3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.5892053973013494</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.696837866446949</v>
-      </c>
       <c r="F3" t="n">
-        <v>0.9486585792100932</v>
+        <v>0.691730395607254</v>
       </c>
       <c r="G3" t="n">
+        <v>0.9227407565936684</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.32</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>48</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>92</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.358695652173913</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2586206896551724</v>
       </c>
     </row>
     <row r="4">
@@ -1234,25 +1621,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.27394533157349</v>
+        <v>28.21319317817688</v>
       </c>
       <c r="D4" t="n">
+        <v>132</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.6785001994415636</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.5843973459545361</v>
-      </c>
       <c r="F4" t="n">
-        <v>0.9619582495477651</v>
+        <v>0.5840716137315201</v>
       </c>
       <c r="G4" t="n">
+        <v>0.9580559228463078</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.2424242424242424</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>32</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>109</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2477064220183486</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="5">
@@ -1267,25 +1663,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53.5795738697052</v>
+        <v>52.83921813964844</v>
       </c>
       <c r="D5" t="n">
+        <v>117</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.9731139646869983</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.9827222339196809</v>
-      </c>
       <c r="F5" t="n">
-        <v>0.9847839852756669</v>
+        <v>0.9805169666245553</v>
       </c>
       <c r="G5" t="n">
+        <v>0.9825214604592835</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>99</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>89</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="6">
@@ -1300,25 +1705,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.43543982505798</v>
+        <v>24.66743159294128</v>
       </c>
       <c r="D6" t="n">
+        <v>78</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.7209690893901419</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.5937434533902246</v>
-      </c>
       <c r="F6" t="n">
-        <v>0.9935288752681102</v>
+        <v>0.5934510889646383</v>
       </c>
       <c r="G6" t="n">
+        <v>0.9926138097555206</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.5256410256410257</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>41</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>57</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="7">
@@ -1333,25 +1747,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.66065096855164</v>
+        <v>30.95514917373657</v>
       </c>
       <c r="D7" t="n">
+        <v>110</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.8617857142857143</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.7894994257999846</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.990859909950015</v>
+        <v>0.7900289637686492</v>
       </c>
       <c r="G7" t="n">
+        <v>0.9920276615334384</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.4363636363636363</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>48</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>70</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="8">
@@ -1366,25 +1789,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55.29569458961487</v>
+        <v>49.72648167610168</v>
       </c>
       <c r="D8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.9949048913043478</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.9892071998212391</v>
-      </c>
       <c r="F8" t="n">
-        <v>0.9892071998212391</v>
+        <v>0.9843365949729397</v>
       </c>
       <c r="G8" t="n">
+        <v>0.9843365949729397</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.7903225806451613</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>98</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>92</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1875</v>
       </c>
     </row>
     <row r="9">
@@ -1399,25 +1831,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.92267990112305</v>
+        <v>24.097984790802</v>
       </c>
       <c r="D9" t="n">
+        <v>115</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.7702834799608993</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.8895458099650471</v>
-      </c>
       <c r="F9" t="n">
-        <v>0.9416100922938329</v>
+        <v>0.8898545732901006</v>
       </c>
       <c r="G9" t="n">
+        <v>0.9425435656639739</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.3826086956521739</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>44</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>93</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="10">
@@ -1432,25 +1873,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38.34892272949219</v>
+        <v>33.90682625770569</v>
       </c>
       <c r="D10" t="n">
+        <v>167</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.7291325695581015</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.8102817458112959</v>
-      </c>
       <c r="F10" t="n">
-        <v>0.8595974535990001</v>
+        <v>0.8106569859834467</v>
       </c>
       <c r="G10" t="n">
+        <v>0.8607711020256499</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.3592814371257485</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>141</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4184397163120567</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="11">
@@ -1465,25 +1915,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.80258131027222</v>
+        <v>21.31533050537109</v>
       </c>
       <c r="D11" t="n">
+        <v>160</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.5372002459520393</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.5409059583400273</v>
-      </c>
       <c r="F11" t="n">
-        <v>0.9650497534110423</v>
+        <v>0.5407418213648125</v>
       </c>
       <c r="G11" t="n">
+        <v>0.9616371924392504</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.1875</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>30</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>119</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2016806722689076</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1463414634146341</v>
       </c>
     </row>
     <row r="12">
@@ -1498,25 +1957,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>49.58110642433167</v>
+        <v>46.42441129684448</v>
       </c>
       <c r="D12" t="n">
+        <v>117</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.9898989898989898</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.9448011901307082</v>
-      </c>
       <c r="F12" t="n">
-        <v>0.9470648925652922</v>
+        <v>0.9363535909536239</v>
       </c>
       <c r="G12" t="n">
+        <v>0.9384804076465</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>90</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>84</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2121212121212121</v>
       </c>
     </row>
     <row r="13">
@@ -1531,25 +1999,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.70360016822815</v>
+        <v>14.46467041969299</v>
       </c>
       <c r="D13" t="n">
+        <v>42</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.8666666666666666</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.8168450032768682</v>
-      </c>
       <c r="F13" t="n">
-        <v>0.9834652773397834</v>
+        <v>0.8163267842454667</v>
       </c>
       <c r="G13" t="n">
+        <v>0.9818461347721047</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>14</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>30</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -1564,25 +2041,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27.43989968299866</v>
+        <v>24.988436460495</v>
       </c>
       <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.7925</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.8796129052316763</v>
-      </c>
       <c r="F14" t="n">
-        <v>0.8547616786151689</v>
+        <v>0.8615116093762567</v>
       </c>
       <c r="G14" t="n">
+        <v>0.8236185049277357</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.34</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>34</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>40</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -1597,25 +2083,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38.69757103919983</v>
+        <v>35.16933059692383</v>
       </c>
       <c r="D15" t="n">
+        <v>79</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.9982456140350878</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.9492964074598156</v>
-      </c>
       <c r="F15" t="n">
-        <v>0.9492964074598156</v>
+        <v>0.9051632885986193</v>
       </c>
       <c r="G15" t="n">
+        <v>0.9051632885986193</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.7721518987341772</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>61</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>60</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="16">
@@ -1630,25 +2125,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>43.44195437431335</v>
+        <v>40.28759622573853</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8946953781512604</v>
+        <v>151</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7562861986639395</v>
+        <v>0.8944327731092436</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9302014923354888</v>
+        <v>0.7532058469308187</v>
       </c>
       <c r="G16" t="n">
+        <v>0.9238806570288861</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.5298013245033113</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>80</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>119</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6554621848739496</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="17">
@@ -1663,16 +2167,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.373984098434448</v>
+        <v>4.904774904251099</v>
       </c>
       <c r="D17" t="n">
+        <v>83</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.9904761904761904</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1686,16 +2195,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.21445751190186</v>
+        <v>10.11806321144104</v>
       </c>
       <c r="D18" t="n">
+        <v>150</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.5892053973013494</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1709,16 +2223,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.36502885818481</v>
+        <v>9.339307308197021</v>
       </c>
       <c r="D19" t="n">
+        <v>132</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.6785001994415636</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1732,16 +2251,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.483864784240723</v>
+        <v>8.740378618240356</v>
       </c>
       <c r="D20" t="n">
+        <v>117</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.9731139646869983</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1755,16 +2279,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.586628198623657</v>
+        <v>4.056405067443848</v>
       </c>
       <c r="D21" t="n">
+        <v>78</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.7209690893901419</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1778,16 +2307,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.312727451324463</v>
+        <v>7.70428991317749</v>
       </c>
       <c r="D22" t="n">
+        <v>110</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.8617857142857143</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1801,16 +2335,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9.196866989135742</v>
+        <v>8.348963260650635</v>
       </c>
       <c r="D23" t="n">
+        <v>124</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.9949048913043478</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1824,16 +2363,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.941753387451172</v>
+        <v>4.470118761062622</v>
       </c>
       <c r="D24" t="n">
+        <v>115</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.7702834799608993</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1847,16 +2391,21 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.06245231628418</v>
+        <v>7.496933937072754</v>
       </c>
       <c r="D25" t="n">
+        <v>167</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.7291325695581015</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1870,16 +2419,21 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.99725604057312</v>
+        <v>6.057881593704224</v>
       </c>
       <c r="D26" t="n">
+        <v>160</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.5372002459520393</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1893,16 +2447,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.968843460083008</v>
+        <v>6.508200168609619</v>
       </c>
       <c r="D27" t="n">
+        <v>117</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.9898989898989898</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1916,16 +2475,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.923839569091797</v>
+        <v>4.463723659515381</v>
       </c>
       <c r="D28" t="n">
+        <v>42</v>
+      </c>
+      <c r="E28" t="n">
         <v>0.8666666666666666</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1939,16 +2503,21 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.609135627746582</v>
+        <v>7.92353081703186</v>
       </c>
       <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
         <v>0.7925</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1962,16 +2531,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.609845161437988</v>
+        <v>6.94684910774231</v>
       </c>
       <c r="D30" t="n">
+        <v>79</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.9982456140350878</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1985,16 +2559,21 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.432675123214722</v>
+        <v>5.784081220626831</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8946953781512604</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8944327731092436</v>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2008,20 +2587,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.11904954910278</v>
+        <v>38.28234767913818</v>
       </c>
       <c r="D32" t="n">
-        <v>0.946031746031746</v>
+        <v>83</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9837489778310913</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.983224793531115</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>63</v>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2035,20 +2619,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>70.24255657196045</v>
+        <v>76.21971821784973</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8746251874062968</v>
+        <v>150</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9489224051900619</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>0.9419040479760119</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9277140245460854</v>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
         <v>92</v>
       </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2062,20 +2651,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>62.75869917869568</v>
+        <v>64.18637037277222</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7742321499800559</v>
+        <v>132</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9679745570552247</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>0.9433585959313922</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9741632146924935</v>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>109</v>
       </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2089,20 +2683,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55.70905876159668</v>
+        <v>52.8313307762146</v>
       </c>
       <c r="D35" t="n">
-        <v>0.804975922953451</v>
+        <v>117</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9848809276006585</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.9979935794542536</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9827717690891338</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="n">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
         <v>89</v>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2116,20 +2715,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37.35616588592529</v>
+        <v>36.79799294471741</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9883040935672514</v>
+        <v>78</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9931404679281509</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+        <v>0.9983291562238931</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9918926216301506</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
         <v>57</v>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2143,20 +2747,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>52.63231182098389</v>
+        <v>55.94428873062134</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8746428571428572</v>
+        <v>110</v>
       </c>
       <c r="E37" t="n">
-        <v>0.991372349903992</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>0.9964285714285714</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9925504519712121</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="n">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
         <v>70</v>
       </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2170,20 +2779,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>58.6241180896759</v>
+        <v>58.9440233707428</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9391983695652174</v>
+        <v>124</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9892071998212391</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9843365949729397</v>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="n">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
         <v>92</v>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2197,20 +2811,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>52.63049077987671</v>
+        <v>52.1801643371582</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9227761485826002</v>
+        <v>115</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9546416657878574</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
+        <v>0.9965786901270772</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9610840247009795</v>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="n">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
         <v>93</v>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2224,20 +2843,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>76.12669992446899</v>
+        <v>76.18641924858093</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8161483906164757</v>
+        <v>167</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8737203556713243</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
+        <v>0.9716312056737588</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.8928610100100525</v>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="n">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
         <v>141</v>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2251,20 +2875,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>73.18037152290344</v>
+        <v>73.24539470672607</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6423447427751587</v>
+        <v>160</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9550177581942121</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>0.8575527772084444</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9512719075879584</v>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
         <v>119</v>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2278,20 +2907,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56.2178840637207</v>
+        <v>54.73534536361694</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8823953823953824</v>
+        <v>117</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9476365729562309</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
+        <v>0.996031746031746</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.939210435214603</v>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="n">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
         <v>84</v>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2305,20 +2939,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21.95231103897095</v>
+        <v>21.68197894096375</v>
       </c>
       <c r="D43" t="n">
-        <v>0.888888888888889</v>
+        <v>42</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9889626240271805</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
+        <v>0.9861111111111112</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9874068243729678</v>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="n">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
         <v>30</v>
       </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2332,20 +2971,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>48.09749269485474</v>
+        <v>46.78516817092896</v>
       </c>
       <c r="D44" t="n">
-        <v>0.79625</v>
+        <v>100</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8766902534926941</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
+        <v>0.97875</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.8517001588294911</v>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
         <v>40</v>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2359,20 +3003,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.04155468940735</v>
+        <v>35.3543803691864</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8280701754385965</v>
+        <v>79</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9492964074598156</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
+        <v>0.9903508771929824</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9051632885986193</v>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="n">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
         <v>60</v>
       </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2386,20 +3035,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>68.96778774261475</v>
+        <v>62.95765161514282</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8529411764705882</v>
+        <v>151</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9362667856678516</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
+        <v>0.9963235294117647</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9310720989574277</v>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
         <v>119</v>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/experiments/hybrid_results/comparison.xlsx
+++ b/experiments/hybrid_results/comparison.xlsx
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32.27287268638611</v>
+        <v>33.03436207771301</v>
       </c>
       <c r="D2" t="n">
         <v>83</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35.61730575561523</v>
+        <v>35.8741090297699</v>
       </c>
       <c r="D3" t="n">
         <v>150</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.21319317817688</v>
+        <v>27.56345438957214</v>
       </c>
       <c r="D4" t="n">
         <v>132</v>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52.83921813964844</v>
+        <v>53.60082101821899</v>
       </c>
       <c r="D5" t="n">
         <v>117</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24.66743159294128</v>
+        <v>24.92256855964661</v>
       </c>
       <c r="D6" t="n">
         <v>78</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.95514917373657</v>
+        <v>32.57445740699768</v>
       </c>
       <c r="D7" t="n">
         <v>110</v>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49.72648167610168</v>
+        <v>54.40395784378052</v>
       </c>
       <c r="D8" t="n">
         <v>124</v>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24.097984790802</v>
+        <v>27.61889600753784</v>
       </c>
       <c r="D9" t="n">
         <v>115</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33.90682625770569</v>
+        <v>37.49147629737854</v>
       </c>
       <c r="D10" t="n">
         <v>167</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.31533050537109</v>
+        <v>22.94651222229004</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>46.42441129684448</v>
+        <v>49.77128744125366</v>
       </c>
       <c r="D12" t="n">
         <v>117</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.46467041969299</v>
+        <v>15.98457622528076</v>
       </c>
       <c r="D13" t="n">
         <v>42</v>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.988436460495</v>
+        <v>27.57102012634277</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35.16933059692383</v>
+        <v>37.67824292182922</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40.28759622573853</v>
+        <v>43.18826770782471</v>
       </c>
       <c r="D16" t="n">
         <v>151</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.904774904251099</v>
+        <v>5.220187187194824</v>
       </c>
       <c r="D17" t="n">
         <v>83</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.11806321144104</v>
+        <v>11.23551630973816</v>
       </c>
       <c r="D18" t="n">
         <v>150</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.339307308197021</v>
+        <v>10.31125521659851</v>
       </c>
       <c r="D19" t="n">
         <v>132</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.740378618240356</v>
+        <v>9.471005201339722</v>
       </c>
       <c r="D20" t="n">
         <v>117</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.056405067443848</v>
+        <v>4.720975875854492</v>
       </c>
       <c r="D21" t="n">
         <v>78</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.70428991317749</v>
+        <v>8.771306991577148</v>
       </c>
       <c r="D22" t="n">
         <v>110</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.348963260650635</v>
+        <v>9.274067401885986</v>
       </c>
       <c r="D23" t="n">
         <v>124</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.470118761062622</v>
+        <v>4.850412607192993</v>
       </c>
       <c r="D24" t="n">
         <v>115</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.496933937072754</v>
+        <v>8.641496658325195</v>
       </c>
       <c r="D25" t="n">
         <v>167</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.057881593704224</v>
+        <v>7.387844800949097</v>
       </c>
       <c r="D26" t="n">
         <v>160</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.508200168609619</v>
+        <v>7.178666591644287</v>
       </c>
       <c r="D27" t="n">
         <v>117</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.463723659515381</v>
+        <v>4.834809064865112</v>
       </c>
       <c r="D28" t="n">
         <v>42</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.92353081703186</v>
+        <v>8.558725833892822</v>
       </c>
       <c r="D29" t="n">
         <v>100</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.94684910774231</v>
+        <v>7.448094606399536</v>
       </c>
       <c r="D30" t="n">
         <v>79</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.784081220626831</v>
+        <v>6.86928129196167</v>
       </c>
       <c r="D31" t="n">
         <v>151</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.28234767913818</v>
+        <v>36.3419361114502</v>
       </c>
       <c r="D32" t="n">
         <v>83</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>76.21971821784973</v>
+        <v>70.5200183391571</v>
       </c>
       <c r="D33" t="n">
         <v>150</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>64.18637037277222</v>
+        <v>60.88948369026184</v>
       </c>
       <c r="D34" t="n">
         <v>132</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>52.8313307762146</v>
+        <v>50.78195381164551</v>
       </c>
       <c r="D35" t="n">
         <v>117</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36.79799294471741</v>
+        <v>33.92947030067444</v>
       </c>
       <c r="D36" t="n">
         <v>78</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55.94428873062134</v>
+        <v>48.64407753944397</v>
       </c>
       <c r="D37" t="n">
         <v>110</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>58.9440233707428</v>
+        <v>56.00828957557678</v>
       </c>
       <c r="D38" t="n">
         <v>124</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>52.1801643371582</v>
+        <v>52.6983585357666</v>
       </c>
       <c r="D39" t="n">
         <v>115</v>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>76.18641924858093</v>
+        <v>74.45982360839844</v>
       </c>
       <c r="D40" t="n">
         <v>167</v>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>73.24539470672607</v>
+        <v>70.68392586708069</v>
       </c>
       <c r="D41" t="n">
         <v>160</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>54.73534536361694</v>
+        <v>55.68229746818542</v>
       </c>
       <c r="D42" t="n">
         <v>117</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21.68197894096375</v>
+        <v>21.07258200645447</v>
       </c>
       <c r="D43" t="n">
         <v>42</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>46.78516817092896</v>
+        <v>46.41818237304688</v>
       </c>
       <c r="D44" t="n">
         <v>100</v>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35.3543803691864</v>
+        <v>39.90585660934448</v>
       </c>
       <c r="D45" t="n">
         <v>79</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>62.95765161514282</v>
+        <v>66.72774839401245</v>
       </c>
       <c r="D46" t="n">
         <v>151</v>
